--- a/verification/cases/roundtrip/header_footer/init.xlsx
+++ b/verification/cases/roundtrip/header_footer/init.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frl\AppData\Local\Temp\xlsx-export-inits-3946636136\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{99EAFAF5-D6D9-4CF7-909D-9A4E5E807E47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="320" yWindow="360" windowWidth="18820" windowHeight="7060"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +22,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -58,14 +64,17 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -103,7 +112,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -175,7 +184,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -348,12 +357,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;CHeader &amp;"-,Bold"Bold&amp;"-,Regular" &amp;U&amp;KFF0000RedUnderlined&amp;U&amp;K01+000 &amp;"-,Bold Italic"Bolditalics</oddHeader>
     <oddFooter>&amp;CFooter &amp;"Arial,Regular"&amp;K03+000ArialBlue&amp;"-,Regular"&amp;K01+000 &amp;"Tahoma,Bold"&amp;K00B050TahomaBoldGreen</oddFooter>
@@ -362,18 +371,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
